--- a/data/trans_bre/P19C06-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C06-Edad-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,29</t>
+          <t>-1,57; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,79</t>
+          <t>-2,03; 0,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,68</t>
+          <t>-1,18; 1,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 0,75</t>
+          <t>-5,0; 0,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 204,45</t>
+          <t>-100,0; 280,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,07</t>
+          <t>-0,89; 1,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,3</t>
+          <t>-1,21; 1,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,64</t>
+          <t>-1,45; 1,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,56</t>
+          <t>-1,34; 1,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,05; 507,87</t>
+          <t>-89,68; 450,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,13; 294,3</t>
+          <t>-75,94; 367,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,75</t>
+          <t>-0,56; 1,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,68</t>
+          <t>-0,23; 2,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,37</t>
+          <t>-0,97; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,36</t>
+          <t>-0,15; 1,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,66; 585,62</t>
+          <t>-54,02; 522,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 438,1</t>
+          <t>-23,73; 479,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,36; 712,7</t>
+          <t>-79,13; 437,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,5</t>
+          <t>0,35; 3,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,06</t>
+          <t>-1,02; 2,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,92</t>
+          <t>-1,91; 1,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,18</t>
+          <t>-0,35; 2,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,26; —</t>
+          <t>-33,11; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 493,4</t>
+          <t>-64,27; 456,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-86,45; 206,91</t>
+          <t>-87,0; 225,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 645,84</t>
+          <t>-33,08; 718,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,35</t>
+          <t>-3,8; 0,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,94</t>
+          <t>-1,14; 2,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,61</t>
+          <t>-1,66; 2,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,56</t>
+          <t>-0,86; 1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 128,75</t>
+          <t>-100,0; 110,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-80,84; 714,9</t>
+          <t>-81,16; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-60,83; 459,97</t>
+          <t>-64,99; 384,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,67; 330,2</t>
+          <t>-49,18; 282,49</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,62</t>
+          <t>-3,04; 0,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,56</t>
+          <t>-1,56; 1,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,39</t>
+          <t>-3,08; 1,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,72</t>
+          <t>-1,54; 0,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-86,71; 160,64</t>
+          <t>-85,94; 146,21</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 0,11</t>
+          <t>-7,22; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,02</t>
+          <t>0,36; 3,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,25</t>
+          <t>-1,56; 3,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,12</t>
+          <t>-0,56; 1,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-83,65; —</t>
+          <t>-79,46; —</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,55</t>
+          <t>-0,59; 0,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,01</t>
+          <t>-0,15; 0,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,76</t>
+          <t>-0,5; 0,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,71</t>
+          <t>-0,42; 0,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,7; 69,27</t>
+          <t>-40,74; 67,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 143,19</t>
+          <t>-15,83; 135,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 85,9</t>
+          <t>-33,05; 85,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 116,68</t>
+          <t>-34,22; 124,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C06-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C06-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-65,86%</t>
+          <t>-49,46%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,33</t>
+          <t>-1,71; 1,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,78</t>
+          <t>-1,93; 0,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,66</t>
+          <t>-1,14; 1,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 0,7</t>
+          <t>-2,92; 1,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 280,3</t>
+          <t>-100,0; 227,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>75,65%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,09</t>
+          <t>-1,05; 1,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,32</t>
+          <t>-1,07; 1,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,55</t>
+          <t>-1,35; 1,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,5</t>
+          <t>-0,8; 1,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,78; 577,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,68; 450,18</t>
+          <t>-86,0; 396,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,94; 367,58</t>
+          <t>-76,53; 431,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>268,25%</t>
+          <t>311,48%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,78</t>
+          <t>-0,63; 1,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,82</t>
+          <t>-0,18; 2,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,32</t>
+          <t>-0,93; 1,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,28</t>
+          <t>-0,07; 1,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,02; 522,18</t>
+          <t>-60,11; 765,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 479,49</t>
+          <t>-24,18; 438,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,13; 437,75</t>
+          <t>-78,84; 427,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>108,68%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,17</t>
+          <t>0,41; 3,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,24</t>
+          <t>-1,16; 2,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,05</t>
+          <t>-1,96; 1,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,06</t>
+          <t>-0,76; 1,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,11; —</t>
+          <t>-25,4; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,27; 456,49</t>
+          <t>-65,84; 385,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,0; 225,72</t>
+          <t>-87,08; 224,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,08; 718,29</t>
+          <t>-46,65; 384,4</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,51</t>
+          <t>-3,87; 0,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,09</t>
+          <t>-1,12; 1,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,61</t>
+          <t>-1,38; 2,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,37</t>
+          <t>-0,61; 1,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 110,68</t>
+          <t>-100,0; 163,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-81,16; —</t>
+          <t>-79,75; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-64,99; 384,32</t>
+          <t>-63,82; 531,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 282,49</t>
+          <t>-45,03; 289,44</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-26,1%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,68</t>
+          <t>-3,19; 0,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,51</t>
+          <t>-1,34; 1,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,28</t>
+          <t>-3,05; 1,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,7</t>
+          <t>-0,96; 1,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,94; 146,21</t>
+          <t>-69,63; 370,93</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,0</t>
+          <t>-6,91; 0,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,37</t>
+          <t>0,36; 3,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,71</t>
+          <t>-1,83; 3,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,12</t>
+          <t>-0,52; 1,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-79,46; —</t>
+          <t>-74,36; —</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,52</t>
+          <t>-0,48; 0,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,99</t>
+          <t>-0,08; 1,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,77</t>
+          <t>-0,47; 0,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,69</t>
+          <t>-0,12; 0,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,74; 67,3</t>
+          <t>-34,54; 77,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 135,73</t>
+          <t>-7,82; 147,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 85,14</t>
+          <t>-31,63; 98,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 124,9</t>
+          <t>-13,8; 138,69</t>
         </is>
       </c>
     </row>
